--- a/Result/profitability/6117.xlsx
+++ b/Result/profitability/6117.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.92125</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>29.5525</v>
+        <v>29.44125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0.86</v>
+        <v>0.7799999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>27.8</v>
+        <v>27.93</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.86875</v>
+        <v>0.8699999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>25.91</v>
+        <v>26.49375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7737499999999999</v>
+        <v>0.78875</v>
       </c>
       <c r="N5" t="n">
-        <v>25.3725</v>
+        <v>25.13625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7274999999999999</v>
+        <v>0.6187499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>23.27125</v>
+        <v>23.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5012499999999999</v>
+        <v>0.3674999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>21.34375</v>
+        <v>20.99625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1393,13 +1393,13 @@
         <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3337499999999999</v>
+        <v>0.2287499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>19.49125</v>
+        <v>18.60875</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6117</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>808</v>
+      </c>
+      <c r="D75" t="n">
+        <v>561</v>
+      </c>
+      <c r="E75" t="n">
+        <v>246</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>94</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.65%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>71</v>
+      </c>
+      <c r="K75" t="n">
+        <v>45</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.535</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.8400000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.631578947368421</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-7.060000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1879659211927583</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3243243243243243</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.890000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05835134300710099</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
